--- a/docs/export/templates/SN101-2024-In-kind.xlsx
+++ b/docs/export/templates/SN101-2024-In-kind.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\home\amice13\GIT\unhcr-app\front\public\export\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\home\amice13\GIT\RAIS-Plus\front\public\export\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E351738-9411-44D6-B668-39584C75A4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96C0C4D-8BD5-4E7B-8912-0C2BFC4586C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{0D83F5B8-BFFE-4C84-84F2-873EAE6BAEAC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="124">
   <si>
     <t>AoR</t>
   </si>
@@ -524,6 +524,24 @@
   </si>
   <si>
     <t>${table:record.items['Transparent plastic sheeting, 3x10m (separate)']}</t>
+  </si>
+  <si>
+    <t>Item 4: Nails 60 (separate)</t>
+  </si>
+  <si>
+    <t>Item 5: Mounting foam, 850ml (separate)</t>
+  </si>
+  <si>
+    <t>Item 6: Screws 4.8x100 (separate)</t>
+  </si>
+  <si>
+    <t>${table:record.items['Nails 60 (separate)']}</t>
+  </si>
+  <si>
+    <t>${table:record.items['Mounting foam, 850ml (separate)']}</t>
+  </si>
+  <si>
+    <t>${table:record.items['Screws 4.8x100 (separate)']}</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE15C91-3DA2-449F-A7C4-9A49A11CFA57}">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="43.1015625" customWidth="1"/>
@@ -1941,13 +1959,13 @@
     <col min="8" max="8" width="12.3125" customWidth="1"/>
     <col min="9" max="9" width="12.1015625" customWidth="1"/>
     <col min="10" max="10" width="13.89453125" customWidth="1"/>
-    <col min="11" max="22" width="7.89453125" customWidth="1"/>
-    <col min="23" max="23" width="6.7890625" customWidth="1"/>
-    <col min="24" max="24" width="47.89453125" customWidth="1"/>
+    <col min="11" max="25" width="7.89453125" customWidth="1"/>
+    <col min="26" max="26" width="6.7890625" customWidth="1"/>
+    <col min="27" max="27" width="47.89453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="1:24" ht="27" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="1:27" ht="27" x14ac:dyDescent="0.85">
       <c r="A2" s="37" t="s">
         <v>106</v>
       </c>
@@ -1967,8 +1985,11 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-    </row>
-    <row r="3" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+    </row>
+    <row r="3" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="3"/>
       <c r="B3" s="41" t="s">
         <v>0</v>
@@ -1990,8 +2011,11 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
-    </row>
-    <row r="4" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+    </row>
+    <row r="4" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A4" s="3"/>
       <c r="B4" s="41" t="s">
         <v>1</v>
@@ -2013,8 +2037,11 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-    </row>
-    <row r="5" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+    </row>
+    <row r="5" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A5" s="4"/>
       <c r="B5" s="44" t="s">
         <v>2</v>
@@ -2040,8 +2067,11 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-    </row>
-    <row r="6" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+    </row>
+    <row r="6" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A6" s="4"/>
       <c r="B6" s="44" t="s">
         <v>3</v>
@@ -2069,8 +2099,11 @@
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-    </row>
-    <row r="7" spans="1:24" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+    </row>
+    <row r="7" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A7" s="4"/>
       <c r="B7" s="44" t="s">
         <v>4</v>
@@ -2092,8 +2125,11 @@
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
-    </row>
-    <row r="8" spans="1:24" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+    </row>
+    <row r="8" spans="1:27" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A8" s="5"/>
       <c r="B8" s="40" t="s">
         <v>5</v>
@@ -2115,8 +2151,11 @@
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
-    </row>
-    <row r="9" spans="1:24" ht="28.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+    </row>
+    <row r="9" spans="1:27" ht="28.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13" t="s">
         <v>6</v>
       </c>
@@ -2145,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ref="L9:W9" si="0">SUM(L$12:L$1000)</f>
+        <f t="shared" ref="L9:Z9" si="0">SUM(L$12:L$1000)</f>
         <v>0</v>
       </c>
       <c r="M9" s="12">
@@ -2192,8 +2231,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="X9" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="15"/>
       <c r="B10" s="53" t="s">
         <v>7</v>
@@ -2224,10 +2275,13 @@
       </c>
       <c r="U10" s="60"/>
       <c r="V10" s="60"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="34"/>
-    </row>
-    <row r="11" spans="1:24" ht="174" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="W10" s="60"/>
+      <c r="X10" s="60"/>
+      <c r="Y10" s="60"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="34"/>
+    </row>
+    <row r="11" spans="1:27" ht="174" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="16" t="s">
         <v>9</v>
       </c>
@@ -2294,14 +2348,23 @@
       <c r="V11" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="W11" s="33" t="s">
+      <c r="W11" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="X11" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y11" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z11" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="X11" s="31" t="s">
+      <c r="AA11" s="31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:27" ht="30" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="26" t="s">
         <v>64</v>
       </c>
@@ -2368,10 +2431,19 @@
       <c r="V12" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="W12" s="52" t="s">
+      <c r="W12" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="X12" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y12" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z12" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="X12" s="21" t="s">
+      <c r="AA12" s="21" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2380,7 +2452,7 @@
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="H10:J10"/>
     <mergeCell ref="L10:S10"/>
-    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="T10:Y10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
